--- a/examples/Scr&Rec_pos_idx_BRAS.xlsx
+++ b/examples/Scr&Rec_pos_idx_BRAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\DEISM\DEISM_main\DEISM\examples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B71A5D-77AB-456B-83E5-EA93A91C3D1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FE84831-38E1-4EE7-83BF-D9E2A1C60428}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,10 +27,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="26">
-  <si>
-    <t>LS: louderspeaker, MP: microphone</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
   <si>
     <t>Index</t>
   </si>
@@ -136,12 +133,49 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Note</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: LS: louderspeaker, MP: microphone;  the positions in .skp files might show slight deviations, so </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>positions in .sofa files as the benchmark</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,6 +208,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -189,7 +231,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -197,17 +239,66 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -236,8 +327,8 @@
       <xdr:rowOff>65689</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>275896</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>284655</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>28447</xdr:rowOff>
     </xdr:to>
@@ -281,8 +372,8 @@
       <xdr:rowOff>35533</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>477345</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>486103</xdr:colOff>
       <xdr:row>24</xdr:row>
       <xdr:rowOff>106159</xdr:rowOff>
     </xdr:to>
@@ -583,245 +674,248 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="16.9140625" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="34.58203125" customWidth="1"/>
+    <col min="10" max="10" width="7.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="20" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="56" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="2"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="E3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0</v>
       </c>
       <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>8</v>
       </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
       <c r="E5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
         <v>12</v>
       </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
       <c r="E6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
         <v>14</v>
       </c>
-      <c r="D7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>4</v>
       </c>
       <c r="B8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
         <v>10</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>5</v>
       </c>
       <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>14</v>
       </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>7</v>
       </c>
       <c r="B11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" t="s">
         <v>10</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>16</v>
       </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>8</v>
       </c>
       <c r="B12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>16</v>
       </c>
-      <c r="D12" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>9</v>
       </c>
       <c r="B13" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" t="s">
         <v>10</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>18</v>
       </c>
-      <c r="D13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>0</v>
       </c>
       <c r="B16" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" t="s">
         <v>6</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>7</v>
       </c>
-      <c r="D16" t="s">
-        <v>8</v>
-      </c>
       <c r="E16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -829,16 +923,16 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
         <v>10</v>
       </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-      <c r="D17" t="s">
-        <v>11</v>
-      </c>
       <c r="E17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -846,16 +940,16 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" t="s">
         <v>12</v>
       </c>
-      <c r="C18" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" t="s">
-        <v>13</v>
-      </c>
       <c r="E18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
@@ -863,16 +957,16 @@
         <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D19" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.3">
@@ -880,16 +974,16 @@
         <v>4</v>
       </c>
       <c r="B20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
         <v>10</v>
       </c>
-      <c r="C20" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" t="s">
-        <v>11</v>
-      </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
@@ -897,16 +991,16 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
         <v>12</v>
       </c>
-      <c r="C21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" t="s">
-        <v>13</v>
-      </c>
       <c r="E21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -914,16 +1008,16 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D22" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
@@ -931,16 +1025,16 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
         <v>10</v>
       </c>
-      <c r="C23" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" t="s">
-        <v>11</v>
-      </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
@@ -948,16 +1042,16 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" t="s">
+        <v>15</v>
+      </c>
+      <c r="D24" t="s">
         <v>12</v>
       </c>
-      <c r="C24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" t="s">
-        <v>13</v>
-      </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
